--- a/call-delivery/intake/2026-07/MOD.xlsx
+++ b/call-delivery/intake/2026-07/MOD.xlsx
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +53,19 @@
     </font>
     <font>
       <color rgb="006B7280"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002E5AAC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -122,7 +134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,7 +143,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +156,26 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I129"/>
+  <dimension ref="B2:N129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -539,12 +571,21 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>CALL DELIVERY  —  Outbound Dialing Schedule (Intake)</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>GROUP STRATEGY &amp; NOTES  (carried over from July 2026 master)</t>
         </is>
       </c>
     </row>
@@ -555,6 +596,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>General Strategy</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -576,6 +624,11 @@
           <t>2026-07</t>
         </is>
       </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>Last 2 Fridays of the month at 12p</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
@@ -593,8 +646,20 @@
           <t>Submitted Date:</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="17" t="n">
         <v>46220</v>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     If LDOM is Friday, will run 2nd &amp; 3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>Runs Preview - 10 seconds</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -638,13 +703,18 @@
           <t>Special Instructions</t>
         </is>
       </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Lists</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="18" t="n">
         <v>46219</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -669,13 +739,28 @@
           <t>Preview (10 seconds)</t>
         </is>
       </c>
+      <c r="K10" s="19" t="inlineStr">
+        <is>
+          <t>List #</t>
+        </is>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="M10" s="19" t="inlineStr">
+        <is>
+          <t>List Specific Strategy</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="18" t="n">
         <v>46226</v>
       </c>
       <c r="D11" s="10" t="n">
@@ -700,13 +785,22 @@
           <t>Preview (10 seconds)</t>
         </is>
       </c>
+      <c r="K11" s="20" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>FMSC_MOD</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="8">
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="18" t="n"/>
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
@@ -719,7 +813,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="18" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="n"/>
@@ -732,7 +826,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="18" t="n"/>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
@@ -745,7 +839,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="18" t="n"/>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
@@ -758,7 +852,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="18" t="n"/>
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="11" t="n"/>
@@ -771,7 +865,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="18" t="n"/>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
@@ -784,7 +878,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="18" t="n"/>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
@@ -797,7 +891,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="18" t="n"/>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="n"/>
@@ -810,7 +904,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="18" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
@@ -823,7 +917,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="18" t="n"/>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="11" t="n"/>
@@ -836,7 +930,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="18" t="n"/>
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="11" t="n"/>
@@ -849,7 +943,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="18" t="n"/>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="11" t="n"/>
@@ -862,7 +956,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="18" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
@@ -875,7 +969,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="18" t="n"/>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
@@ -888,7 +982,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C26" s="9" t="n"/>
+      <c r="C26" s="18" t="n"/>
       <c r="D26" s="10" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="11" t="n"/>
@@ -901,7 +995,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C27" s="9" t="n"/>
+      <c r="C27" s="18" t="n"/>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
@@ -914,7 +1008,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C28" s="9" t="n"/>
+      <c r="C28" s="18" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
@@ -927,7 +1021,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C29" s="9" t="n"/>
+      <c r="C29" s="18" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="11" t="n"/>
@@ -940,7 +1034,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C30" s="9" t="n"/>
+      <c r="C30" s="18" t="n"/>
       <c r="D30" s="10" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="11" t="n"/>
@@ -953,7 +1047,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C31" s="9" t="n"/>
+      <c r="C31" s="18" t="n"/>
       <c r="D31" s="10" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
@@ -966,7 +1060,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C32" s="9" t="n"/>
+      <c r="C32" s="18" t="n"/>
       <c r="D32" s="10" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="11" t="n"/>
@@ -979,7 +1073,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C33" s="9" t="n"/>
+      <c r="C33" s="18" t="n"/>
       <c r="D33" s="10" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="11" t="n"/>
@@ -992,7 +1086,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C34" s="9" t="n"/>
+      <c r="C34" s="18" t="n"/>
       <c r="D34" s="10" t="n"/>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="11" t="n"/>
@@ -1005,7 +1099,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C35" s="9" t="n"/>
+      <c r="C35" s="18" t="n"/>
       <c r="D35" s="10" t="n"/>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="11" t="n"/>
@@ -1018,7 +1112,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C36" s="9" t="n"/>
+      <c r="C36" s="18" t="n"/>
       <c r="D36" s="10" t="n"/>
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="11" t="n"/>
@@ -1031,7 +1125,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C37" s="9" t="n"/>
+      <c r="C37" s="18" t="n"/>
       <c r="D37" s="10" t="n"/>
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="11" t="n"/>
@@ -1044,7 +1138,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C38" s="9" t="n"/>
+      <c r="C38" s="18" t="n"/>
       <c r="D38" s="10" t="n"/>
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="11" t="n"/>
@@ -1057,7 +1151,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C39" s="9" t="n"/>
+      <c r="C39" s="18" t="n"/>
       <c r="D39" s="10" t="n"/>
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="11" t="n"/>
@@ -1070,7 +1164,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C40" s="9" t="n"/>
+      <c r="C40" s="18" t="n"/>
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="11" t="n"/>
@@ -1083,7 +1177,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C41" s="9" t="n"/>
+      <c r="C41" s="18" t="n"/>
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="11" t="n"/>
@@ -1096,7 +1190,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C42" s="9" t="n"/>
+      <c r="C42" s="18" t="n"/>
       <c r="D42" s="10" t="n"/>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
@@ -1109,7 +1203,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="n"/>
+      <c r="C43" s="18" t="n"/>
       <c r="D43" s="10" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="n"/>
@@ -1122,7 +1216,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C44" s="9" t="n"/>
+      <c r="C44" s="18" t="n"/>
       <c r="D44" s="10" t="n"/>
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="11" t="n"/>
@@ -1135,7 +1229,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="18" t="n"/>
       <c r="D45" s="10" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
@@ -1148,7 +1242,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C46" s="9" t="n"/>
+      <c r="C46" s="18" t="n"/>
       <c r="D46" s="10" t="n"/>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
@@ -1161,7 +1255,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C47" s="9" t="n"/>
+      <c r="C47" s="18" t="n"/>
       <c r="D47" s="10" t="n"/>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="11" t="n"/>
@@ -1174,7 +1268,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C48" s="9" t="n"/>
+      <c r="C48" s="18" t="n"/>
       <c r="D48" s="10" t="n"/>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
@@ -1187,7 +1281,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C49" s="9" t="n"/>
+      <c r="C49" s="18" t="n"/>
       <c r="D49" s="10" t="n"/>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="11" t="n"/>
@@ -1200,7 +1294,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C50" s="9" t="n"/>
+      <c r="C50" s="18" t="n"/>
       <c r="D50" s="10" t="n"/>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
@@ -1213,7 +1307,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C51" s="9" t="n"/>
+      <c r="C51" s="18" t="n"/>
       <c r="D51" s="10" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
@@ -1226,7 +1320,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C52" s="9" t="n"/>
+      <c r="C52" s="18" t="n"/>
       <c r="D52" s="10" t="n"/>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
@@ -1239,7 +1333,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C53" s="9" t="n"/>
+      <c r="C53" s="18" t="n"/>
       <c r="D53" s="10" t="n"/>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
@@ -1252,7 +1346,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C54" s="9" t="n"/>
+      <c r="C54" s="18" t="n"/>
       <c r="D54" s="10" t="n"/>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
@@ -1265,7 +1359,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C55" s="9" t="n"/>
+      <c r="C55" s="18" t="n"/>
       <c r="D55" s="10" t="n"/>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="11" t="n"/>
@@ -1278,7 +1372,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C56" s="9" t="n"/>
+      <c r="C56" s="18" t="n"/>
       <c r="D56" s="10" t="n"/>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="11" t="n"/>
@@ -1291,7 +1385,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C57" s="9" t="n"/>
+      <c r="C57" s="18" t="n"/>
       <c r="D57" s="10" t="n"/>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="11" t="n"/>
@@ -1304,7 +1398,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C58" s="9" t="n"/>
+      <c r="C58" s="18" t="n"/>
       <c r="D58" s="10" t="n"/>
       <c r="E58" s="11" t="n"/>
       <c r="F58" s="11" t="n"/>
@@ -1317,7 +1411,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C59" s="9" t="n"/>
+      <c r="C59" s="18" t="n"/>
       <c r="D59" s="10" t="n"/>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="11" t="n"/>
@@ -1330,7 +1424,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C60" s="9" t="n"/>
+      <c r="C60" s="18" t="n"/>
       <c r="D60" s="10" t="n"/>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
@@ -1343,7 +1437,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C61" s="9" t="n"/>
+      <c r="C61" s="18" t="n"/>
       <c r="D61" s="10" t="n"/>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="11" t="n"/>
@@ -1356,7 +1450,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C62" s="9" t="n"/>
+      <c r="C62" s="18" t="n"/>
       <c r="D62" s="10" t="n"/>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
@@ -1369,7 +1463,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C63" s="9" t="n"/>
+      <c r="C63" s="18" t="n"/>
       <c r="D63" s="10" t="n"/>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
@@ -1382,7 +1476,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C64" s="9" t="n"/>
+      <c r="C64" s="18" t="n"/>
       <c r="D64" s="10" t="n"/>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
@@ -1395,7 +1489,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C65" s="9" t="n"/>
+      <c r="C65" s="18" t="n"/>
       <c r="D65" s="10" t="n"/>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
@@ -1408,7 +1502,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C66" s="9" t="n"/>
+      <c r="C66" s="18" t="n"/>
       <c r="D66" s="10" t="n"/>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
@@ -1421,7 +1515,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C67" s="9" t="n"/>
+      <c r="C67" s="18" t="n"/>
       <c r="D67" s="10" t="n"/>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
@@ -1434,7 +1528,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C68" s="9" t="n"/>
+      <c r="C68" s="18" t="n"/>
       <c r="D68" s="10" t="n"/>
       <c r="E68" s="11" t="n"/>
       <c r="F68" s="11" t="n"/>
@@ -1447,7 +1541,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C69" s="9" t="n"/>
+      <c r="C69" s="18" t="n"/>
       <c r="D69" s="10" t="n"/>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
@@ -1460,7 +1554,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C70" s="9" t="n"/>
+      <c r="C70" s="18" t="n"/>
       <c r="D70" s="10" t="n"/>
       <c r="E70" s="11" t="n"/>
       <c r="F70" s="11" t="n"/>
@@ -1473,7 +1567,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C71" s="9" t="n"/>
+      <c r="C71" s="18" t="n"/>
       <c r="D71" s="10" t="n"/>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
@@ -1486,7 +1580,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C72" s="9" t="n"/>
+      <c r="C72" s="18" t="n"/>
       <c r="D72" s="10" t="n"/>
       <c r="E72" s="11" t="n"/>
       <c r="F72" s="11" t="n"/>
@@ -1499,7 +1593,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C73" s="9" t="n"/>
+      <c r="C73" s="18" t="n"/>
       <c r="D73" s="10" t="n"/>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
@@ -1512,7 +1606,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C74" s="9" t="n"/>
+      <c r="C74" s="18" t="n"/>
       <c r="D74" s="10" t="n"/>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
@@ -1525,7 +1619,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C75" s="9" t="n"/>
+      <c r="C75" s="18" t="n"/>
       <c r="D75" s="10" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
@@ -1538,7 +1632,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C76" s="9" t="n"/>
+      <c r="C76" s="18" t="n"/>
       <c r="D76" s="10" t="n"/>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
@@ -1551,7 +1645,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C77" s="9" t="n"/>
+      <c r="C77" s="18" t="n"/>
       <c r="D77" s="10" t="n"/>
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="11" t="n"/>
@@ -1564,7 +1658,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C78" s="9" t="n"/>
+      <c r="C78" s="18" t="n"/>
       <c r="D78" s="10" t="n"/>
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="11" t="n"/>
@@ -1577,7 +1671,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C79" s="9" t="n"/>
+      <c r="C79" s="18" t="n"/>
       <c r="D79" s="10" t="n"/>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
@@ -1590,7 +1684,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C80" s="9" t="n"/>
+      <c r="C80" s="18" t="n"/>
       <c r="D80" s="10" t="n"/>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
@@ -1603,7 +1697,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="n"/>
+      <c r="C81" s="18" t="n"/>
       <c r="D81" s="10" t="n"/>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
@@ -1616,7 +1710,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="n"/>
+      <c r="C82" s="18" t="n"/>
       <c r="D82" s="10" t="n"/>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
@@ -1629,7 +1723,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C83" s="9" t="n"/>
+      <c r="C83" s="18" t="n"/>
       <c r="D83" s="10" t="n"/>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
@@ -1642,7 +1736,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C84" s="9" t="n"/>
+      <c r="C84" s="18" t="n"/>
       <c r="D84" s="10" t="n"/>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
@@ -1655,7 +1749,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C85" s="9" t="n"/>
+      <c r="C85" s="18" t="n"/>
       <c r="D85" s="10" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
@@ -1668,7 +1762,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C86" s="9" t="n"/>
+      <c r="C86" s="18" t="n"/>
       <c r="D86" s="10" t="n"/>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
@@ -1681,7 +1775,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C87" s="9" t="n"/>
+      <c r="C87" s="18" t="n"/>
       <c r="D87" s="10" t="n"/>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
@@ -1694,7 +1788,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C88" s="9" t="n"/>
+      <c r="C88" s="18" t="n"/>
       <c r="D88" s="10" t="n"/>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
@@ -1707,7 +1801,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C89" s="9" t="n"/>
+      <c r="C89" s="18" t="n"/>
       <c r="D89" s="10" t="n"/>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
@@ -1720,7 +1814,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C90" s="9" t="n"/>
+      <c r="C90" s="18" t="n"/>
       <c r="D90" s="10" t="n"/>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
@@ -1733,7 +1827,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C91" s="9" t="n"/>
+      <c r="C91" s="18" t="n"/>
       <c r="D91" s="10" t="n"/>
       <c r="E91" s="11" t="n"/>
       <c r="F91" s="11" t="n"/>
@@ -1746,7 +1840,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C92" s="9" t="n"/>
+      <c r="C92" s="18" t="n"/>
       <c r="D92" s="10" t="n"/>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
@@ -1759,7 +1853,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C93" s="9" t="n"/>
+      <c r="C93" s="18" t="n"/>
       <c r="D93" s="10" t="n"/>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
@@ -1772,7 +1866,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C94" s="9" t="n"/>
+      <c r="C94" s="18" t="n"/>
       <c r="D94" s="10" t="n"/>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
@@ -1785,7 +1879,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C95" s="9" t="n"/>
+      <c r="C95" s="18" t="n"/>
       <c r="D95" s="10" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
@@ -1798,7 +1892,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C96" s="9" t="n"/>
+      <c r="C96" s="18" t="n"/>
       <c r="D96" s="10" t="n"/>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
@@ -1811,7 +1905,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C97" s="9" t="n"/>
+      <c r="C97" s="18" t="n"/>
       <c r="D97" s="10" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
@@ -1824,7 +1918,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C98" s="9" t="n"/>
+      <c r="C98" s="18" t="n"/>
       <c r="D98" s="10" t="n"/>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
@@ -1837,7 +1931,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C99" s="9" t="n"/>
+      <c r="C99" s="18" t="n"/>
       <c r="D99" s="10" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
@@ -1850,7 +1944,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C100" s="9" t="n"/>
+      <c r="C100" s="18" t="n"/>
       <c r="D100" s="10" t="n"/>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
@@ -1863,7 +1957,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C101" s="9" t="n"/>
+      <c r="C101" s="18" t="n"/>
       <c r="D101" s="10" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
@@ -1876,7 +1970,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C102" s="9" t="n"/>
+      <c r="C102" s="18" t="n"/>
       <c r="D102" s="10" t="n"/>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
@@ -1889,7 +1983,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C103" s="9" t="n"/>
+      <c r="C103" s="18" t="n"/>
       <c r="D103" s="10" t="n"/>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
@@ -1902,7 +1996,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C104" s="9" t="n"/>
+      <c r="C104" s="18" t="n"/>
       <c r="D104" s="10" t="n"/>
       <c r="E104" s="11" t="n"/>
       <c r="F104" s="11" t="n"/>
@@ -1915,7 +2009,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C105" s="9" t="n"/>
+      <c r="C105" s="18" t="n"/>
       <c r="D105" s="10" t="n"/>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
@@ -1928,7 +2022,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C106" s="9" t="n"/>
+      <c r="C106" s="18" t="n"/>
       <c r="D106" s="10" t="n"/>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
@@ -1941,7 +2035,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C107" s="9" t="n"/>
+      <c r="C107" s="18" t="n"/>
       <c r="D107" s="10" t="n"/>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
@@ -1954,7 +2048,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C108" s="9" t="n"/>
+      <c r="C108" s="18" t="n"/>
       <c r="D108" s="10" t="n"/>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
@@ -1967,7 +2061,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C109" s="9" t="n"/>
+      <c r="C109" s="18" t="n"/>
       <c r="D109" s="10" t="n"/>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
@@ -1980,7 +2074,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C110" s="9" t="n"/>
+      <c r="C110" s="18" t="n"/>
       <c r="D110" s="10" t="n"/>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
@@ -1993,7 +2087,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C111" s="9" t="n"/>
+      <c r="C111" s="18" t="n"/>
       <c r="D111" s="10" t="n"/>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
@@ -2006,7 +2100,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C112" s="9" t="n"/>
+      <c r="C112" s="18" t="n"/>
       <c r="D112" s="10" t="n"/>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
@@ -2019,7 +2113,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C113" s="9" t="n"/>
+      <c r="C113" s="18" t="n"/>
       <c r="D113" s="10" t="n"/>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
@@ -2032,7 +2126,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C114" s="9" t="n"/>
+      <c r="C114" s="18" t="n"/>
       <c r="D114" s="10" t="n"/>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
@@ -2045,7 +2139,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C115" s="9" t="n"/>
+      <c r="C115" s="18" t="n"/>
       <c r="D115" s="10" t="n"/>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
@@ -2058,7 +2152,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C116" s="9" t="n"/>
+      <c r="C116" s="18" t="n"/>
       <c r="D116" s="10" t="n"/>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
@@ -2071,7 +2165,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C117" s="9" t="n"/>
+      <c r="C117" s="18" t="n"/>
       <c r="D117" s="10" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
@@ -2084,7 +2178,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C118" s="9" t="n"/>
+      <c r="C118" s="18" t="n"/>
       <c r="D118" s="10" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
@@ -2097,7 +2191,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C119" s="9" t="n"/>
+      <c r="C119" s="18" t="n"/>
       <c r="D119" s="10" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="11" t="n"/>
@@ -2110,7 +2204,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C120" s="9" t="n"/>
+      <c r="C120" s="18" t="n"/>
       <c r="D120" s="10" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
@@ -2123,7 +2217,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C121" s="9" t="n"/>
+      <c r="C121" s="18" t="n"/>
       <c r="D121" s="10" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="11" t="n"/>
@@ -2136,7 +2230,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C122" s="9" t="n"/>
+      <c r="C122" s="18" t="n"/>
       <c r="D122" s="10" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="11" t="n"/>
@@ -2149,7 +2243,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C123" s="9" t="n"/>
+      <c r="C123" s="18" t="n"/>
       <c r="D123" s="10" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="11" t="n"/>
@@ -2162,7 +2256,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C124" s="9" t="n"/>
+      <c r="C124" s="18" t="n"/>
       <c r="D124" s="10" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
@@ -2175,7 +2269,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C125" s="9" t="n"/>
+      <c r="C125" s="18" t="n"/>
       <c r="D125" s="10" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
@@ -2188,7 +2282,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C126" s="9" t="n"/>
+      <c r="C126" s="18" t="n"/>
       <c r="D126" s="10" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="11" t="n"/>
@@ -2201,7 +2295,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C127" s="9" t="n"/>
+      <c r="C127" s="18" t="n"/>
       <c r="D127" s="10" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="11" t="n"/>
@@ -2214,7 +2308,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C128" s="9" t="n"/>
+      <c r="C128" s="18" t="n"/>
       <c r="D128" s="10" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="11" t="n"/>
@@ -2227,7 +2321,7 @@
         <f>IF($C$5="","",$C$5)</f>
         <v/>
       </c>
-      <c r="C129" s="9" t="n"/>
+      <c r="C129" s="18" t="n"/>
       <c r="D129" s="10" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="11" t="n"/>
@@ -2236,9 +2330,14 @@
       <c r="I129" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K5:N5"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
